--- a/data-collection/netty-data.xlsx
+++ b/data-collection/netty-data.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/data-collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5405D9F7-EBD3-4DE9-9F85-2D62701AFF5E}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C82AD0-2764-42D4-B1D9-9BD7CEB1CEB0}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="-11640" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="333">
   <si>
     <t>Wersja</t>
   </si>
@@ -556,12 +567,483 @@
   </si>
   <si>
     <t>4.0.0</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Jan 14, 2025</t>
+  </si>
+  <si>
+    <t>Dec 17, 2024</t>
+  </si>
+  <si>
+    <t>Nov 12, 2024</t>
+  </si>
+  <si>
+    <t>Oct 01, 2024</t>
+  </si>
+  <si>
+    <t>Sep 04, 2024</t>
+  </si>
+  <si>
+    <t>Jul 19, 2024</t>
+  </si>
+  <si>
+    <t>Jun 11, 2024</t>
+  </si>
+  <si>
+    <t>May 22, 2024</t>
+  </si>
+  <si>
+    <t>Apr 15, 2024</t>
+  </si>
+  <si>
+    <t>Mar 21, 2024</t>
+  </si>
+  <si>
+    <t>Feb 13, 2024</t>
+  </si>
+  <si>
+    <t>Jan 19, 2024</t>
+  </si>
+  <si>
+    <t>Jan 16, 2024</t>
+  </si>
+  <si>
+    <t>Dec 15, 2023</t>
+  </si>
+  <si>
+    <t>Dec 13, 2023</t>
+  </si>
+  <si>
+    <t>Nov 09, 2023</t>
+  </si>
+  <si>
+    <t>Oct 10, 2023</t>
+  </si>
+  <si>
+    <t>Sep 28, 2023</t>
+  </si>
+  <si>
+    <t>Sep 21, 2023</t>
+  </si>
+  <si>
+    <t>Aug 23, 2023</t>
+  </si>
+  <si>
+    <t>Jul 27, 2023</t>
+  </si>
+  <si>
+    <t>Jul 20, 2023</t>
+  </si>
+  <si>
+    <t>Jun 20, 2023</t>
+  </si>
+  <si>
+    <t>May 25, 2023</t>
+  </si>
+  <si>
+    <t>Apr 25, 2023</t>
+  </si>
+  <si>
+    <t>Apr 03, 2023</t>
+  </si>
+  <si>
+    <t>Mar 14, 2023</t>
+  </si>
+  <si>
+    <t>Feb 13, 2023</t>
+  </si>
+  <si>
+    <t>Feb 12, 2023</t>
+  </si>
+  <si>
+    <t>Jan 12, 2023</t>
+  </si>
+  <si>
+    <t>Dec 12, 2022</t>
+  </si>
+  <si>
+    <t>Nov 09, 2022</t>
+  </si>
+  <si>
+    <t>Oct 12, 2022</t>
+  </si>
+  <si>
+    <t>Oct 11, 2022</t>
+  </si>
+  <si>
+    <t>Sep 13, 2022</t>
+  </si>
+  <si>
+    <t>Sep 08, 2022</t>
+  </si>
+  <si>
+    <t>Aug 26, 2022</t>
+  </si>
+  <si>
+    <t>Jul 11, 2022</t>
+  </si>
+  <si>
+    <t>Jun 14, 2022</t>
+  </si>
+  <si>
+    <t>May 06, 2022</t>
+  </si>
+  <si>
+    <t>Apr 12, 2022</t>
+  </si>
+  <si>
+    <t>Mar 10, 2022</t>
+  </si>
+  <si>
+    <t>Feb 08, 2022</t>
+  </si>
+  <si>
+    <t>Jan 12, 2022</t>
+  </si>
+  <si>
+    <t>Dec 13, 2021</t>
+  </si>
+  <si>
+    <t>Dec 09, 2021</t>
+  </si>
+  <si>
+    <t>Nov 03, 2021</t>
+  </si>
+  <si>
+    <t>Oct 11, 2021</t>
+  </si>
+  <si>
+    <t>Sep 09, 2021</t>
+  </si>
+  <si>
+    <t>Aug 16, 2021</t>
+  </si>
+  <si>
+    <t>Jul 16, 2021</t>
+  </si>
+  <si>
+    <t>May 19, 2021</t>
+  </si>
+  <si>
+    <t>May 17, 2021</t>
+  </si>
+  <si>
+    <t>Apr 01, 2021</t>
+  </si>
+  <si>
+    <t>Mar 30, 2021</t>
+  </si>
+  <si>
+    <t>Mar 09, 2021</t>
+  </si>
+  <si>
+    <t>Feb 08, 2021</t>
+  </si>
+  <si>
+    <t>Jan 13, 2021</t>
+  </si>
+  <si>
+    <t>Jan 12, 2021</t>
+  </si>
+  <si>
+    <t>Dec 17, 2020</t>
+  </si>
+  <si>
+    <t>Dec 08, 2020</t>
+  </si>
+  <si>
+    <t>Nov 11, 2020</t>
+  </si>
+  <si>
+    <t>Oct 13, 2020</t>
+  </si>
+  <si>
+    <t>Sep 08, 2020</t>
+  </si>
+  <si>
+    <t>Jul 09, 2020</t>
+  </si>
+  <si>
+    <t>May 13, 2020</t>
+  </si>
+  <si>
+    <t>Apr 22, 2020</t>
+  </si>
+  <si>
+    <t>Mar 17, 2020</t>
+  </si>
+  <si>
+    <t>Mar 09, 2020</t>
+  </si>
+  <si>
+    <t>Feb 28, 2020</t>
+  </si>
+  <si>
+    <t>Jan 13, 2020</t>
+  </si>
+  <si>
+    <t>Dec 18, 2019</t>
+  </si>
+  <si>
+    <t>Oct 24, 2019</t>
+  </si>
+  <si>
+    <t>Sep 27, 2019</t>
+  </si>
+  <si>
+    <t>Sep 12, 2019</t>
+  </si>
+  <si>
+    <t>Aug 13, 2019</t>
+  </si>
+  <si>
+    <t>Jul 24, 2019</t>
+  </si>
+  <si>
+    <t>Jun 28, 2019</t>
+  </si>
+  <si>
+    <t>Apr 30, 2019</t>
+  </si>
+  <si>
+    <t>Apr 17, 2019</t>
+  </si>
+  <si>
+    <t>Mar 08, 2019</t>
+  </si>
+  <si>
+    <t>Jan 21, 2019</t>
+  </si>
+  <si>
+    <t>Nov 29, 2018</t>
+  </si>
+  <si>
+    <t>Oct 30, 2018</t>
+  </si>
+  <si>
+    <t>Sep 28, 2018</t>
+  </si>
+  <si>
+    <t>Aug 24, 2018</t>
+  </si>
+  <si>
+    <t>Jul 27, 2018</t>
+  </si>
+  <si>
+    <t>Jul 11, 2018</t>
+  </si>
+  <si>
+    <t>Jul 10, 2018</t>
+  </si>
+  <si>
+    <t>May 14, 2018</t>
+  </si>
+  <si>
+    <t>Apr 19, 2018</t>
+  </si>
+  <si>
+    <t>Apr 04, 2018</t>
+  </si>
+  <si>
+    <t>Feb 21, 2018</t>
+  </si>
+  <si>
+    <t>Feb 05, 2018</t>
+  </si>
+  <si>
+    <t>Jan 21, 2018</t>
+  </si>
+  <si>
+    <t>Dec 15, 2017</t>
+  </si>
+  <si>
+    <t>Dec 08, 2017</t>
+  </si>
+  <si>
+    <t>Nov 08, 2017</t>
+  </si>
+  <si>
+    <t>Sep 25, 2017</t>
+  </si>
+  <si>
+    <t>Aug 24, 2017</t>
+  </si>
+  <si>
+    <t>Aug 02, 2017</t>
+  </si>
+  <si>
+    <t>Jul 06, 2017</t>
+  </si>
+  <si>
+    <t>Jun 08, 2017</t>
+  </si>
+  <si>
+    <t>May 11, 2017</t>
+  </si>
+  <si>
+    <t>Apr 29, 2017</t>
+  </si>
+  <si>
+    <t>Mar 10, 2017</t>
+  </si>
+  <si>
+    <t>Jan 30, 2017</t>
+  </si>
+  <si>
+    <t>Jan 12, 2017</t>
+  </si>
+  <si>
+    <t>Oct 14, 2016</t>
+  </si>
+  <si>
+    <t>Aug 29, 2016</t>
+  </si>
+  <si>
+    <t>Jul 27, 2016</t>
+  </si>
+  <si>
+    <t>Jul 15, 2016</t>
+  </si>
+  <si>
+    <t>Jul 01, 2016</t>
+  </si>
+  <si>
+    <t>Jun 07, 2016</t>
+  </si>
+  <si>
+    <t>May 25, 2016</t>
+  </si>
+  <si>
+    <t>Nov 09, 2017</t>
+  </si>
+  <si>
+    <t>Sep 21, 2017</t>
+  </si>
+  <si>
+    <t>Jun 09, 2017</t>
+  </si>
+  <si>
+    <t>Apr 04, 2016</t>
+  </si>
+  <si>
+    <t>Mar 21, 2016</t>
+  </si>
+  <si>
+    <t>Jan 29, 2016</t>
+  </si>
+  <si>
+    <t>Nov 03, 2015</t>
+  </si>
+  <si>
+    <t>Sep 30, 2015</t>
+  </si>
+  <si>
+    <t>Sep 02, 2015</t>
+  </si>
+  <si>
+    <t>Jul 24, 2015</t>
+  </si>
+  <si>
+    <t>Jun 23, 2015</t>
+  </si>
+  <si>
+    <t>May 07, 2015</t>
+  </si>
+  <si>
+    <t>Apr 02, 2015</t>
+  </si>
+  <si>
+    <t>Mar 02, 2015</t>
+  </si>
+  <si>
+    <t>Dec 31, 2014</t>
+  </si>
+  <si>
+    <t>Oct 29, 2014</t>
+  </si>
+  <si>
+    <t>Aug 15, 2014</t>
+  </si>
+  <si>
+    <t>Aug 14, 2014</t>
+  </si>
+  <si>
+    <t>Jul 01, 2014</t>
+  </si>
+  <si>
+    <t>Jun 12, 2014</t>
+  </si>
+  <si>
+    <t>Apr 30, 2014</t>
+  </si>
+  <si>
+    <t>Apr 01, 2014</t>
+  </si>
+  <si>
+    <t>Feb 24, 2014</t>
+  </si>
+  <si>
+    <t>Feb 20, 2014</t>
+  </si>
+  <si>
+    <t>Jan 21, 2014</t>
+  </si>
+  <si>
+    <t>Dec 22, 2013</t>
+  </si>
+  <si>
+    <t>Nov 28, 2013</t>
+  </si>
+  <si>
+    <t>Nov 07, 2013</t>
+  </si>
+  <si>
+    <t>Oct 21, 2013</t>
+  </si>
+  <si>
+    <t>Oct 03, 2013</t>
+  </si>
+  <si>
+    <t>Sep 06, 2013</t>
+  </si>
+  <si>
+    <t>Aug 26, 2013</t>
+  </si>
+  <si>
+    <t>Aug 08, 2013</t>
+  </si>
+  <si>
+    <t>Aug 01, 2013</t>
+  </si>
+  <si>
+    <t>Jul 31, 2013</t>
+  </si>
+  <si>
+    <t>Jul 23, 2013</t>
+  </si>
+  <si>
+    <t>Jul 18, 2013</t>
+  </si>
+  <si>
+    <t>Jul 17, 2013</t>
+  </si>
+  <si>
+    <t>Jul 16, 2013</t>
+  </si>
+  <si>
+    <t>Jul 15, 2013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -591,8 +1073,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -877,1414 +1361,1945 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B176"/>
+  <dimension ref="A1:C176"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B47">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>48</v>
       </c>
-      <c r="B48">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
-      <c r="B49">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B50">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B51">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>52</v>
       </c>
-      <c r="B52">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
-      <c r="B53">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>54</v>
       </c>
-      <c r="B54">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C54">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>55</v>
       </c>
-      <c r="B55">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C55">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>56</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>57</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C57">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>59</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C59">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>60</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>61</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C61">
         <v>6.2</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>62</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C62">
         <v>6.2</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63">
         <v>6.2</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>64</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C64">
         <v>6.2</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>65</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C65">
         <v>6.2</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>66</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66">
         <v>6.2</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>67</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C67">
         <v>6.2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>68</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68">
         <v>6.2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>69</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C69">
         <v>6.2</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>70</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70">
         <v>6.2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>71</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C71">
         <v>6.2</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>72</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C72">
         <v>6.2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73">
         <v>6.2</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>74</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C74">
         <v>6.35</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>75</v>
       </c>
-      <c r="B75">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B75" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C75">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>76</v>
       </c>
-      <c r="B76">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B76" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C76">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>77</v>
       </c>
-      <c r="B77">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>78</v>
       </c>
-      <c r="B78">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C78">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>79</v>
       </c>
-      <c r="B79">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C79">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>80</v>
       </c>
-      <c r="B80">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C80">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>81</v>
       </c>
-      <c r="B81">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B81" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C81">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>82</v>
       </c>
-      <c r="B82">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C82">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
-      <c r="B83">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B83" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C83">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>84</v>
       </c>
-      <c r="B84">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>85</v>
       </c>
-      <c r="B85">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B85" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C85">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>86</v>
       </c>
-      <c r="B86">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C86">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>87</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C87">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>88</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>89</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C89">
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>90</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C90">
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>91</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C91">
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>92</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C92">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>93</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93">
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>94</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C94">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>95</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95">
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>96</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C96">
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>97</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C97">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>98</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C98">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>99</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C99">
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>100</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C100">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>101</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C101">
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>102</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C102">
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>103</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103">
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>104</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C104">
         <v>6.2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>105</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C105">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>106</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C106">
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>107</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C107">
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>108</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108">
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>109</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C109">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>110</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C110">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>111</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C111">
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>112</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C112">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>113</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C113">
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>114</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C114">
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>115</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C115">
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>116</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C116">
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>117</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C117">
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>118</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C118">
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>119</v>
       </c>
-      <c r="B119">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B119" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C119">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>120</v>
       </c>
-      <c r="B120">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B120" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C120">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>121</v>
       </c>
-      <c r="B121">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B121" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C121">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>122</v>
       </c>
-      <c r="B122">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B122" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C122">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>123</v>
       </c>
-      <c r="B123">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B123" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C123">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>124</v>
       </c>
-      <c r="B124">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B124" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C124">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>125</v>
       </c>
-      <c r="B125">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B125" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C125">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>126</v>
       </c>
-      <c r="B126">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C126">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>127</v>
       </c>
-      <c r="B127">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B127" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>128</v>
       </c>
-      <c r="B128">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B128" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C128">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>129</v>
       </c>
-      <c r="B129">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B129" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>130</v>
       </c>
-      <c r="B130">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B130" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C130">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>131</v>
       </c>
-      <c r="B131">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B131" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C131">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>132</v>
       </c>
-      <c r="B132">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B132" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C132">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>133</v>
       </c>
-      <c r="B133">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B133" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C133">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>134</v>
       </c>
-      <c r="B134">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B134" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C134">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>135</v>
       </c>
-      <c r="B135">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B135" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>136</v>
       </c>
-      <c r="B136">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B136" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C136">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>137</v>
       </c>
-      <c r="B137">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B137" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C137">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>138</v>
       </c>
-      <c r="B138">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B138" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C138">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>139</v>
       </c>
-      <c r="B139">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B139" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C139">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>140</v>
       </c>
-      <c r="B140">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B140" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>141</v>
       </c>
-      <c r="B141">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B141" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C141">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>142</v>
       </c>
-      <c r="B142">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B142" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C142">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>143</v>
       </c>
-      <c r="B143">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B143" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C143">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>144</v>
       </c>
-      <c r="B144">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B144" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C144">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>145</v>
       </c>
-      <c r="B145">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B145" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>146</v>
       </c>
-      <c r="B146">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B146" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>147</v>
       </c>
-      <c r="B147">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B147" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>148</v>
       </c>
-      <c r="B148">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B148" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C148">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>149</v>
       </c>
-      <c r="B149">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B149" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C149">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>150</v>
       </c>
-      <c r="B150">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B150" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>151</v>
       </c>
-      <c r="B151">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B151" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C151">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>152</v>
       </c>
-      <c r="B152">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B152" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C152">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>153</v>
       </c>
-      <c r="B153">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B153" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C153">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>154</v>
       </c>
-      <c r="B154">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B154" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C154">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>155</v>
       </c>
-      <c r="B155">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B155" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>156</v>
       </c>
-      <c r="B156">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B156" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>157</v>
       </c>
-      <c r="B157">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B157" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C157">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>158</v>
       </c>
-      <c r="B158">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B158" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>159</v>
       </c>
-      <c r="B159">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B159" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>160</v>
       </c>
-      <c r="B160">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B160" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>161</v>
       </c>
-      <c r="B161">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C161">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>162</v>
       </c>
-      <c r="B162">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C162">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>163</v>
       </c>
-      <c r="B163">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B163" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C163">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>164</v>
       </c>
-      <c r="B164">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B164" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C164">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>165</v>
       </c>
-      <c r="B165">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B165" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C165">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>166</v>
       </c>
-      <c r="B166">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B166" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C166">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>167</v>
       </c>
-      <c r="B167">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B167" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C167">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>168</v>
       </c>
-      <c r="B168">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B168" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C168">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>169</v>
       </c>
-      <c r="B169">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B169" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C169">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>170</v>
       </c>
-      <c r="B170">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B170" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C170">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>171</v>
       </c>
-      <c r="B171">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B171" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C171">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>172</v>
       </c>
-      <c r="B172">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B172" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C172">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>173</v>
       </c>
-      <c r="B173">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B173" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C173">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>174</v>
       </c>
-      <c r="B174">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B174" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C174">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>175</v>
       </c>
-      <c r="B175">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B175" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C175">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>176</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C176">
         <v>6.5</v>
       </c>
     </row>
